--- a/manuscript/supplementary_data_1_datasets.xlsx
+++ b/manuscript/supplementary_data_1_datasets.xlsx
@@ -8,15 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Datasets" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Analysis_roles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Column_definitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Configurations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Analysis_roles" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Column_definitions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datasets'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Analysis_roles'!$A$1:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Column_definitions'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sources'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datasets'!$A$1:$Q$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Configurations'!$A$1:$M$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Analysis_roles'!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Column_definitions'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sources'!$A$1:$E$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,29 +452,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="44" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="31" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dataset</t>
@@ -485,77 +487,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Protein length (aa)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>UniProt</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Perturbation modality</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Assay</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cell context</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Protein length (aa)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>UniProt</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Original data deposit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Obtained here from</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Perturbations as published</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cells as published</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Perturbations scored here (n)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Cells scored here</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Median cells per perturbation (here)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Original data deposit</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Obtained here from</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>DOI</t>
         </is>
       </c>
     </row>
@@ -570,72 +572,72 @@
           <t>Primary (allele-resolved)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P04637</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Protein-coding variant (allele)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Perturb-seq</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>A549 (lung adenocarcinoma)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>393</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>P04637</t>
-        </is>
-      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>GEO GSE161824</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>GEO GSE161824</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Ursu et al. 2022, Nature Biotechnology 40:896-905</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41587-021-01160-7</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>83422</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>929</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>GEO GSE161824</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>GEO GSE161824</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Ursu et al. 2022, Nature Biotechnology 40:896-905</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>10.1038/s41587-021-01160-7</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -649,72 +651,72 @@
           <t>Primary (allele-resolved)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P01116</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Protein-coding variant (allele)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Perturb-seq</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>A549 (lung adenocarcinoma)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>P01116</t>
-        </is>
-      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>GEO GSE161824</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>GEO GSE161824</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Ursu et al. 2022, Nature Biotechnology 40:896-905</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41587-021-01160-7</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>83556</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>1000</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>GEO GSE161824</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>GEO GSE161824</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Ursu et al. 2022, Nature Biotechnology 40:896-905</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>10.1038/s41587-021-01160-7</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -728,72 +730,72 @@
           <t>Primary (allele-resolved)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P15976</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Protein-coding variant (allele)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Base editing (Perturb-BE-seq)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Human haematopoietic stem and progenitor cells</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>413</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>P15976</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>GEO GSE215253</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Processed matrix and holdout splits distributed with PerturbNet (Hugging Face cyclopeta/PerturbNet_reproduce)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Martin-Rufino et al. 2023, Cell 186:2456-2474.e24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.cell.2023.03.035</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>254</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>149161</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>354</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>GEO GSE215253</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Processed matrix and holdout splits distributed with PerturbNet (Hugging Face cyclopeta/PerturbNet_reproduce)</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Martin-Rufino et al. 2023, Cell 186:2456-2474.e24</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.cell.2023.03.035</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -807,72 +809,72 @@
           <t>Primary (allele-resolved)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>1154</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P23458</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Protein-coding variant (allele)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>scSNV-seq</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>HT-29 (colorectal), interferon-gamma stimulated</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>1154</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>P23458</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>ENA PRJEB48915</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Processed objects from Zenodo record 10418435</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Cooper et al. 2024, Genome Biology 25:20</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10.1186/s13059-024-03169-y</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>NOT_VERIFIED</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>4904</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>104</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>ENA PRJEB48915</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Processed objects from Zenodo record 10418435</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Cooper et al. 2024, Genome Biology 25:20</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>10.1186/s13059-024-03169-y</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -888,75 +890,75 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>CRISPRi gene knockdown (dCas9-KRAB)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Perturb-seq (single-cell CRISPR screen)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>K562 (chronic myeloid leukaemia)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t>GEO GSE90546</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>scPerturb data portal</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Adamson et al. 2016, Cell 167:1867-1882.e21</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>10.1016/j.cell.2016.11.048</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
           <t>91 sgRNAs targeting 82 genes (unfolded protein response screen)</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Reported per experiment; no study-wide total stated</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>GEO GSE90546</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>scPerturb data portal</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>93</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>Adamson et al. 2016, Cell 167:1867-1882.e21</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.cell.2016.11.048</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
@@ -973,75 +975,75 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
           <t>CRISPRa, single and paired (SunTag)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Perturb-seq (single-cell CRISPR screen)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>K562 (chronic myeloid leukaemia)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
+          <t>GEO GSE133344</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>scPerturb data portal</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Norman et al. 2019, Science 365:786-793</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>10.1126/science.aax4438</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
           <t>287 perturbations</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>~110,000 cells (median 273 per condition) in the pooled experiment</t>
         </is>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>236</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>GEO GSE133344</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>scPerturb data portal</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>195</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>Norman et al. 2019, Science 365:786-793</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>10.1126/science.aax4438</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
@@ -1058,82 +1060,82 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>CRISPRi gene knockdown, genome-scale</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Perturb-seq (single-cell CRISPR screen)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>K562 and RPE1</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>K562 (essential-gene screen)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>9,866 expressed genes (K562 day-8 genome-scale screen)</t>
+          <t>SRA BioProject PRJNA831566 (no GEO accession); processed data at figshare+ 10.25452/figshare.plus.20029387</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>scPerturb data portal (ReplogleWeissman2022_K562_essential.h5ad)</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Replogle et al. 2022, Cell 185:2559-2575.e28</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>10.1016/j.cell.2022.05.013</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>9,866 expressed genes in the genome-scale study</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>&gt;2.5 million cells</t>
         </is>
       </c>
-      <c r="K8" s="3" t="n">
-        <v>1832</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>SRA BioProject PRJNA831566 (no GEO accession); processed data at figshare+ 10.25452/figshare.plus.20029387</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>scPerturb data portal</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>414</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Replogle et al. 2022, Cell 185:2559-2575.e28</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.cell.2022.05.013</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>VCC</t>
+          <t>KOLF2.1J</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1143,82 +1145,82 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>CRISPRi gene knockdown (dual-guide dCas9-KRAB)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Single-cell CRISPR screen (Virtual Cell Challenge training split)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>H1 human embryonic stem cells</t>
+          <t>CRISPRi gene knockdown</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
+          <t>Single-cell CRISPR screen</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>KOLF2.1J human induced pluripotent stem cells</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>150 target genes in the training split (of 300 total)</t>
+          <t>SRA BioProject PRJNA1173491; processed data at figshare+ 10.25452/figshare.plus.27261219</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>183,097 cells over the 150 training targets (sum of the official pert_counts_Training.csv; excludes non-targeting controls)</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>145</v>
+          <t>Processed KOLF2.1J pan-genome AnnData</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Nourreddine et al. 2026, Nature Biotechnology</t>
+        </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>10.1038/s41587-026-03199-w</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>Genome-wide CRISPRi perturbation atlas</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Arc Virtual Cell Atlas, Google Cloud Storage bucket; no INSDC accession</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Arc Virtual Cell Atlas</t>
-        </is>
+          <t>2,659,209 cells in the pan-genome file</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>1500</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Roohani et al. 2025, Cell 188:3370-3374</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.cell.2025.06.008</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>sci-Plex</t>
+          <t>VCC</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1228,82 +1230,82 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Small molecule, 188 compounds at four doses</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>sci-Plex (sci-RNA-seq with nuclear hashing)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>A549, K562 and MCF7 in the main screen</t>
+          <t>CRISPRi gene knockdown (dual-guide dCas9-KRAB)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>Single-cell CRISPR screen (Virtual Cell Challenge training split)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>H1 human embryonic stem cells</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>188 compounds, each at four doses</t>
+          <t>Arc Virtual Cell Atlas, Google Cloud Storage bucket; no INSDC accession</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>649,340 cells</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>188</v>
+          <t>Arc Virtual Cell Atlas training data</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Roohani et al. 2025, Cell 188:3370-3374</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>10.1016/j.cell.2025.06.008</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>150 target genes in the training split (of 300 total)</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>GEO GSE139944</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>GEO GSE139944</t>
-        </is>
+          <t>183,097 cells over the 150 training targets (excluding non-targeting controls)</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>139</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Srivatsan et al. 2020, Science 367:45-51</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>10.1126/science.aax6234</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>McFarland</t>
+          <t>Papalexi</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1313,165 +1315,760 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Small molecule (13 drugs) and CRISPR (GPX4)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>MIX-Seq (pooled cell lines, SNP demultiplexing)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Pools of 24 to 99 cancer cell lines</t>
+          <t>CRISPR perturbation</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t>ECCITE-seq (RNA and surface-protein readouts)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>THP-1 human monocytic cells</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>13 drugs plus one CRISPR target gene (GPX4)</t>
+          <t>GEO GSE153056</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Reported per experiment; no study-wide total stated</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>10</v>
+          <t>scPerturb data portal (PapalexiSatija2021_eccite_RNA.h5ad and protein.h5ad)</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Papalexi et al. 2021, Nature Genetics</t>
+        </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>10.1038/s41588-021-00778-2</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>CRISPR perturbation screen</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>figshare 10.6084/m9.figshare.10298696</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>figshare</t>
-        </is>
+          <t>20,729 cells in the analyzed resource</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>McFarland et al. 2020, Nature Communications 11:4296</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>10.1038/s41467-020-17440-w</t>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>PerturbMulti</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Pooled genetic perturbation (CRISPR)</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Single-cell RNA-seq and imaging-derived intensity readouts</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Mouse liver, pooled CRISPR screen</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Hugging Face xingjiepan/PerturbMulti</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>RNA_scaled_crispr_screen_20240615.h5ad and protein_intensities_crispr_screen_20240615.h5ad</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Saunders et al. 2025, Cell</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>10.1016/j.cell.2025.05.022</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Pooled CRISPR screen (RNA and imaging readouts)</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Branch-specific; see Configurations sheet</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Frangieh</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>CRISPR perturbation</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Perturb-CITE-seq (RNA and surface-protein readouts)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Melanoma models: control, IFN-gamma and co-culture contexts</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Single Cell Portal SCP1064</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>scPerturb data portal (FrangiehIzar2021_RNA.h5ad and protein.h5ad)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Frangieh et al. 2021, Nature Genetics</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>10.1038/s41588-021-00779-1</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>248 perturbation units across three contexts</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>218,331 cells in the analyzed resource</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>X-Atlas</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>CRISPRi gene knockdown (dual-guide)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Single-cell RNA-seq (X-Atlas/Orion)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>HCT116 and HEK293T human cell lines</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Processed data DOI 10.25452/figshare.plus.29190726</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Xaira-Therapeutics/X-Atlas-Orion processed data</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Huang et al. 2025, bioRxiv</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>10.1101/2025.06.11.659105</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Genome-wide gene-target perturbation atlas</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>7,943,468 cells across HCT116 and HEK293T</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GSE306429</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Small molecule</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Single-cell RNA-seq perturbation screen</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>A549, A375 and CD34+ strata (selected configurations)</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>GEO GSE306429</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>GSE306429_combined_demuxed.h5ad</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>DeMeo et al. 2025, Science</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>10.1126/science.adi8577</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>103 compounds</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>1,257,778 cells in the combined demultiplexed file</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Tahoe-100M</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Broader perturbation screen</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Small molecule</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Single-cell drug atlas (subset used here)</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>50 cancer cell lines</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Single-cell drug atlas</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>50 cancer cell lines; selected CVCL strata</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Hugging Face tahoebio/Tahoe-100M and Arc Virtual Cell Atlas; no INSDC accession</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M selected strata and demonstration subset</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Zhang et al. 2025, bioRxiv</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>10.1101/2025.02.20.639398</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>1,100 small-molecule perturbations (379 distinct drugs)</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>~100 million transcriptomic profiles</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>1075</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>1,100 small-molecule perturbations (379 distinct drugs)</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>~100 million transcriptomic profiles</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>NOT_VERIFIED</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Hugging Face tahoebio/Tahoe-100M and Arc Virtual Cell Atlas; no INSDC accession</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>Arc Virtual Cell Atlas</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Zhang et al. 2025, bioRxiv</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>10.1101/2025.02.20.639398</t>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Small molecule, 188 compounds at four doses</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex (sci-RNA-seq with nuclear hashing)</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>A549, K562 and MCF7 at 24 h (selected configurations)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>GEO GSE139944</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>scPerturb data portal (SrivatsanTrapnell2020_sciplex3.h5ad)</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Srivatsan et al. 2020, Science 367:45-51</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>10.1126/science.aax6234</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>188 compounds, each at four doses</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>649,340 cells in the main screen</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>735</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>McFarland</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Small molecule (chemical-perturbation subset)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>MIX-Seq (pooled cell lines, SNP demultiplexing)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Pools of 24 to 99 cancer cell lines</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>figshare 10.6084/m9.figshare.10298696</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>PertPy_data/mcfarland_gene_pert.h5ad demonstration subset</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>McFarland et al. 2020, Nature Communications 11:4296</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-020-17440-w</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>13 drugs plus one CRISPR target gene (GPX4) in the source study</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>182,875-cell parent; this paper uses a 5,500-cell, 10-condition demonstration subset</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Cytokine</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M single-cell RNA-seq</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Human PBMC donors (selected donor strata)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Parse Biosciences 10M human PBMC cytokines dataset</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Parse_10M_PBMC_cytokines.h5ad</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Parse Biosciences, 10M human PBMC cytokines dataset</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>90 cytokine perturbations per donor stratum</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>9,697,974 cells in the full cytokine file</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>See Configurations sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1482,559 +2079,1884 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Configuration ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Resource</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Benchmark-ranking resolution (Fig. 5c)</t>
+          <t>Configuration/context</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Rankability predictor, LODO (Fig. 6b,c)</t>
+          <t>Stratum</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pilot-to-evaluation validation (Fig. 6d)</t>
+          <t>Perturbation class</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Frozen packaged criterion (Fig. 6h)</t>
+          <t>Readout</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Native-vs-depth-matched atlas comparison (Fig. 6f)</t>
+          <t>Reference condition</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Arms entered (n)</t>
+          <t>Input file / subset</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Panel arm</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Perturbations scored (n)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Cells scored</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Control cells</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Source result record</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TP53</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Primary (allele-resolved)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>adamson2016</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Adamson</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Gal4-4(mod)_pBA582</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>AdamsonWeissman2016_GSM2406681_10X010.h5ad</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>prespecified</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>KRAS</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Primary (allele-resolved)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>frangieh_protein_Coculture</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Frangieh</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Co-culture / protein</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Co-culture</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>FrangiehIzar2021_protein.h5ad</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>73114</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>18334</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/frangieh_protein_Coculture.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>GATA1</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Primary (allele-resolved)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>frangieh_protein_Control</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Frangieh</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Control / protein</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>FrangiehIzar2021_protein.h5ad</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>57627</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>15361</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/frangieh_protein_Control.json</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>JAK1</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Primary (allele-resolved)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>frangieh_protein_IFNg</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Frangieh</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>IFNγ / protein</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>IFNγ</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>FrangiehIzar2021_protein.h5ad</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>87590</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>23910</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/frangieh_protein_IFNg.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Adamson</t>
+          <t>frangieh_rna_Coculture</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>Frangieh</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Co-culture / RNA</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Co-culture</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>genetic</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>control</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>FrangiehIzar2021_RNA.h5ad</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>73114</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>18334</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/frangieh_rna_Coculture.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Norman</t>
+          <t>frangieh_rna_Control</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>Frangieh</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Control / RNA</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>genetic</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>control</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>FrangiehIzar2021_RNA.h5ad</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>57627</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>15361</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/frangieh_rna_Control.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Replogle</t>
+          <t>frangieh_rna_IFNg</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>Frangieh</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>IFNγ / RNA</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>IFNγ</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>genetic</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>control</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>FrangiehIzar2021_RNA.h5ad</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>87590</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>23910</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/frangieh_rna_IFNg.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>VCC</t>
+          <t>gse306429_A375</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>GSE306429</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A375</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A375</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DMSO</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>GSE306429_combined_demuxed.h5ad</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>184414</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>21347</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/gse306429_A375.json</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>sci-Plex</t>
+          <t>gse306429_A549</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>GSE306429</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A549</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A549</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DMSO</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>GSE306429_combined_demuxed.h5ad</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>171110</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>18780</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/gse306429_A549.json</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>McFarland</t>
+          <t>gse306429_CD34</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>GSE306429</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CD34+</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CD34+</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DMSO</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>GSE306429_combined_demuxed.h5ad</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>173548</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>18354</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/gse306429_CD34.json</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Tahoe-100M</t>
+          <t>kolf_ipsc</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Broader perturbation screen</t>
+          <t>KOLF2.1J</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>genetic</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NTC</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>subsets/kolf_k1500.npz</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>564835</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>146747</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/kolf_ipsc.json</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Datasets in arm (n)</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr"/>
+          <t>mcfarland</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>McFarland</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>chemical</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>RNA</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>PertPy_data/mcfarland_gene_pert.h5ad</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>prespecified</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>norman2019</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Norman</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>NormanWeissman2019_filtered.h5ad</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>prespecified</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>papalexi_protein</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Papalexi</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>PapalexiSatija2021_eccite_protein.h5ad</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>20729</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>2386</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/papalexi_protein.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>papalexi_rna</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Papalexi</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>PapalexiSatija2021_eccite_RNA.h5ad</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>20729</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>2386</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/papalexi_rna.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>parse10m_Donor1</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>cytokine</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>PBS</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>subsets/parse_Donor1</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1267690</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>90452</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/parse10m_Donor1.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>parse10m_Donor12</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>cytokine</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>PBS</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>subsets/parse_Donor12</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>1054708</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>71179</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/parse10m_Donor12.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>parse10m_Donor5</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>cytokine</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>PBS</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>subsets/parse_Donor5</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1066725</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>55293</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/parse10m_Donor5.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>perturbmulti_protein</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>PerturbMulti</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>protein_intensities_crispr_screen_20240615.h5ad</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>97928</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>5137</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/perturbmulti_protein.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>perturbmulti_rna</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>PerturbMulti</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>RNA_scaled_crispr_screen_20240615.h5ad</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>79179</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>4161</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/perturbmulti_rna.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>replogle</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Replogle</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>control (inferred)</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>ReplogleWeissman2022_K562_essential.h5ad</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>prespecified</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>tahoe100m</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>dmso_tf|0.0</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M demonstration subset</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>prespecified</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>tahoe100m_CVCL_0459</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>dmso_tf|0.0</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>subsets/tahoe_CVCL_0459</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1075</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>5943050</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>131593</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/tahoe100m_CVCL_0459.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>tahoe100m_CVCL_0480</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>dmso_tf|0.0</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>subsets/tahoe_CVCL_0480</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>1075</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>4170504</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>97098</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/tahoe100m_CVCL_0480.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>tahoe100m_CVCL_0546</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>dmso_tf|0.0</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>subsets/tahoe_CVCL_0546</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1075</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>6363927</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>147988</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/tahoe100m_CVCL_0546.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>vcc_training</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>VCC</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>non-targeting</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>adata_Training.h5ad</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>prespecified</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>xatlas_hct116</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>X-Atlas</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Non-Targeting</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>subsets/xatlas_hct116_k1500.npz</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>634070</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>165777</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/xatlas_hct116.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>xatlas_hek293t</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>X-Atlas</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>whole resource</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>genetic</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Non-Targeting</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>subsets/xatlas_hek293t_k1500</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>761697</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>218838</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/xatlas_hek293t.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>sciplex3_A549_24h</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>A549 / 24.0</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>A549 / 24.0</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>control, 0.0</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>SrivatsanTrapnell2020_sciplex3.h5ad</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>162171</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>3773</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/sciplex3_A549_24h.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>sciplex3_K562_24h</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>K562 / 24.0</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>K562 / 24.0</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>control, 0.0</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>SrivatsanTrapnell2020_sciplex3.h5ad</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>173652</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>3935</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/sciplex3_K562_24h.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>sciplex3_MCF7_24h</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>MCF7 / 24.0</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>MCF7 / 24.0</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>RNA</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>control, 0.0</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>SrivatsanTrapnell2020_sciplex3.h5ad</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>additional</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>735</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>344862</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>7786</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>results/resolution_panel_v2/panel/sciplex3_MCF7_24h.json</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:M32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2045,147 +3967,817 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Term</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Allele-resolved prediction (Figs. 1-4)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Broader panel, 31 configurations (Fig. 5a-e)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prespecified six-screen identification (Fig. 5f)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pilot rankability / repeated-pilot aggregate (Fig. 6b)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Native-vs-depth-matched atlas comparison (Fig. 6f)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Arms entered (n)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Primary datasets are the allele-resolved screens in which the measurement-resolution criterion is defined. Broader perturbation screens test whether it holds beyond alleles.</t>
-        </is>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TP53</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Primary (allele-resolved)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Perturbations as published</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Scale reported by the original study. Verified from a primary source for the seven external screens only; see the Sources sheet.</t>
-        </is>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>KRAS</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Primary (allele-resolved)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cells as published</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>As above. Where a study reports only per-experiment figures and no study-wide total, that is stated instead of a total summed here.</t>
-        </is>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GATA1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Primary (allele-resolved)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Perturbations scored here (n)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>For allele datasets, the variant conditions in the benchmark. For external screens, the largest count across the arms it enters; the arms apply different inclusion thresholds and depths, so a single number would be misleading. Per-arm counts are in the manuscript Supplementary Tables.</t>
-        </is>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>JAK1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Primary (allele-resolved)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Cells scored here</t>
+          <t>Adamson</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Includes the dataset wild-type or control cells for the allele datasets, matching the manuscript Methods.</t>
-        </is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Original data deposit</t>
+          <t>Norman</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Where the original study deposited the data, which is not always where this study obtained it.</t>
-        </is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Obtained here from</t>
+          <t>Replogle</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The route actually used in this study.</t>
-        </is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>NOT_VERIFIED</t>
+          <t>KOLF2.1J</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The value was not confirmed from a source that was retrieved. It is left blank on purpose rather than filled from a secondary summary.</t>
-        </is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Results are not in this workbook</t>
+          <t>VCC</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Per-dataset measured quantities are in the manuscript Supplementary Information: Supplementary Table 5 (per-gene backbone and reproducibility ceiling), Supplementary Table 6 (signal and noise), Supplementary Table 7 (depth prescriptions) and Supplementary Table 9 (the pre-registered panel).</t>
-        </is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Numbering</t>
+          <t>Papalexi</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nature Portfolio numbers Supplementary Tables and Supplementary Data as separate series. The Supplementary Information PDF holds Supplementary Tables 1-10; this workbook is Supplementary Data 1.</t>
-        </is>
-      </c>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PerturbMulti</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Frangieh</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>X-Atlas</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>GSE306429</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>McFarland</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Broader perturbation screen</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Datasets/resources in arm (n)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>31 configurations / 14 resources</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2196,17 +4788,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>This workbook describes 18 named resources: four primary allele-resolved datasets and 14 broader perturbation resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Configurations</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>The Configurations sheet lists the 31 resource-context-readout configurations used in the broader panel (26 RNA and 5 protein). Configurations nested in one resource are not independent resources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Perturbations as published</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Scale reported by the original study or public resource. This is distinct from the configuration-specific scored counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Cells as published</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Published resource scale. Where a resource contains multiple contexts or readouts, the resource-level value is not summed across configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Perturbations scored here (n)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>For allele datasets, the number of variant conditions. For broader resources, the largest n among that resource's analyzed configurations; exact configuration counts are on Configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Cells scored here</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Allele rows include the dataset-specific wild-type/control cells. Broader resources are reported per configuration because contexts/readouts can overlap; see Configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Original data deposit</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Where the original study deposited the data, which is not always where this study obtained it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Obtained here from</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>The route or processed file actually used in this study, stated at resource level; exact input/subset names are on Configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>NOT_VERIFIED</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>The value was not confirmed from a retrieved source and is deliberately not asserted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Results are not in this workbook</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Detection, identification, reproducibility, model-performance and depth results remain in Supplementary Tables 3-6 and the released machine-readable result files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Numbering</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Nature Portfolio numbers Supplementary Tables and Supplementary Data separately. This standalone workbook is Supplementary Data 1.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kind</t>
@@ -2214,7 +4969,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>Dataset/resource</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2246,12 +5001,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>cell context, modality, perturbations, accession</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -2273,12 +5028,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>repository record GSE90546</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2300,12 +5055,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>cell context, modality, 287 perturbations, ~110,000 cells, accession</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2327,12 +5082,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>repository record GSE133344</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2354,12 +5109,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>cell lines, modality, 9,866 genes, &gt;2.5M cells, SRA-only deposit</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -2381,12 +5136,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BioProject PRJNA831566; no linked GEO series</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -2403,22 +5158,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>VCC</t>
+          <t>KOLF2.1J</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>H1 hESC, training split, hosting</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ArcInstitute/arc-virtual-cell-atlas/blob/main/virtual-cell-challenge/README.md</t>
+          <t>https://www.nature.com/articles/s41587-026-03199-w</t>
         </is>
       </c>
     </row>
@@ -2430,22 +5185,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VCC</t>
+          <t>KOLF2.1J</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>150 training targets and 183,097 cells (column sum of the official file)</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://storage.googleapis.com/arc-institute-virtual-cell-atlas/virtual-cell-challenge/2025/</t>
+          <t>https://doi.org/10.25452/figshare.plus.27261219</t>
         </is>
       </c>
     </row>
@@ -2457,22 +5212,22 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>VCC</t>
+          <t>KOLF2.1J</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>CRISPRi dual-guide modality</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>stated in secondary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://arcinstitute.org/news/behind-the-data-virtual-cell-challenge</t>
+          <t>https://www.ncbi.nlm.nih.gov/bioproject/PRJNA1173491</t>
         </is>
       </c>
     </row>
@@ -2489,17 +5244,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>venue, volume, pages, DOI</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://api.crossref.org/works/10.1016/j.cell.2025.06.008</t>
+          <t>https://github.com/ArcInstitute/arc-virtual-cell-atlas/tree/main/virtual-cell-challenge</t>
         </is>
       </c>
     </row>
@@ -2511,22 +5266,22 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>sci-Plex</t>
+          <t>VCC</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>three main-screen cell lines, 188 compounds, 649,340 cells</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7289078/</t>
+          <t>https://doi.org/10.1016/j.cell.2025.06.008</t>
         </is>
       </c>
     </row>
@@ -2538,22 +5293,22 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>sci-Plex</t>
+          <t>Papalexi</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>repository record GSE139944</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE139944</t>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE153056</t>
         </is>
       </c>
     </row>
@@ -2565,22 +5320,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>McFarland</t>
+          <t>Papalexi</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24-99 cell-line pools, 13 drugs plus GPX4 CRISPR, no study-wide cell total</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7453022/</t>
+          <t>https://doi.org/10.1038/s41588-021-00778-2</t>
         </is>
       </c>
     </row>
@@ -2592,22 +5347,22 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>McFarland</t>
+          <t>PerturbMulti</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>figshare deposit 10298696</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://figshare.com/articles/dataset/MIX-seq_data/10298696</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/12324982/</t>
         </is>
       </c>
     </row>
@@ -2619,22 +5374,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Tahoe-100M</t>
+          <t>PerturbMulti</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>50 cell lines, 1,100 perturbations, ~100M profiles</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/2025.02.20.639398v1.full</t>
+          <t>https://huggingface.co/datasets/xingjiepan/PerturbMulti</t>
         </is>
       </c>
     </row>
@@ -2646,212 +5401,513 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tahoe-100M</t>
+          <t>Frangieh</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>hosting; no INSDC accession</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>stated in primary source</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/tahoebio/Tahoe-100M</t>
+          <t>https://singlecell.broadinstitute.org/single_cell/study/SCP1064</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Measured in this study</t>
+          <t>External metadata</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>all allele datasets</t>
+          <t>Frangieh</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>perturbations scored, cells scored, median depth</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>computed from a committed result file</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>data/allele_perturb_bench.csv, via manuscript/figures/nm_style.load_bench</t>
+          <t>https://doi.org/10.1038/s41588-021-00779-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Measured in this study</t>
+          <t>External metadata</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Adamson, Norman, Replogle, VCC, sci-Plex</t>
+          <t>X-Atlas</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>perturbations scored in the benchmark-ranking arm</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>computed from a committed result file</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>results/benchmark_resolution/summary.csv</t>
+          <t>https://huggingface.co/datasets/Xaira-Therapeutics/X-Atlas-Orion</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Measured in this study</t>
+          <t>External metadata</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Adamson, Norman, Replogle and the four allele datasets</t>
+          <t>X-Atlas</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>perturbations scored in the rankability predictor</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>computed from a committed result file</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>results/rankability_predictor_honest.csv</t>
+          <t>https://doi.org/10.25452/figshare.plus.29190726</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Measured in this study</t>
+          <t>External metadata</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Adamson, Norman, Replogle</t>
+          <t>X-Atlas</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>perturbations in the prospective pilot arm</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>computed from a committed result file</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>results/fig6_derived/prospective_auc.csv</t>
+          <t>https://doi.org/10.1101/2025.06.11.659105</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Measured in this study</t>
+          <t>External metadata</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Adamson, Norman, Replogle, VCC, McFarland, Tahoe-100M</t>
+          <t>GSE306429</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>perturbations scored under the frozen criterion</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>computed from a committed result file</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>results/canonical/resolution_panel.csv</t>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE306429</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Measured in this study</t>
+          <t>External metadata</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Adamson, Norman, Replogle</t>
+          <t>GSE306429</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>depth-matched atlas comparison membership</t>
+          <t>resource metadata, deposit or publication</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>computed from a committed result file</t>
+          <t>public source</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>results/fig6_derived/depthmatch_summary.csv</t>
+          <t>https://doi.org/10.1126/science.adi8577</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/tahoebio/Tahoe-100M</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Tahoe-100M</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1101/2025.02.20.639398</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE139944</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>sci-Plex 3</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1126/science.aax6234</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>McFarland</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41467-020-17440-w</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>McFarland</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://figshare.com/articles/dataset/MIX-seq_data/10298696</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>External metadata</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Parse 10M</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>resource metadata, deposit or publication</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>public source</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.parsebiosciences.com/datasets/10-million-human-pbmcs-in-a-single-experiment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>Primary allele datasets</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>assay, cell context, accession, protein length</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>stated in the manuscript Methods</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>manuscript/latex/AllelePerturb_manuscript.tex, Benchmark construction and Data availability</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>TP53/KRAS</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>assay, context, accession</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>manuscript Methods/Data availability</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE161824</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Primary allele datasets</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>GATA1</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>assay, accession, processed matrix</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>manuscript Methods/Data availability</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/geo/query/acc.cgi?acc=GSE215253</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Primary allele datasets</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>JAK1</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>assay, accession, processed object</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>manuscript Methods/Data availability</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.10418435</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Measured in this study</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>all allele datasets</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>variant counts, cell counts, median depth</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>committed benchmark table</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>data/allele_perturb_bench.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Measured in this study</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>broader panel</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>31 configuration manifest and per-configuration counts</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>committed panel table</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>results/canonical/resolution_panel_v2_table.csv</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E24"/>
+  <autoFilter ref="A1:E35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>